--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36488-2025 artfynd.xlsx
+++ b/artfynd/A 36488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225082</v>
       </c>
       <c r="B2" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
